--- a/songs/DontStopTheMusic_v1/quelle/struktur.xlsx
+++ b/songs/DontStopTheMusic_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>118</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(7374, 5)   (Matrix: progScrollText("Dont stop the music by Rihanna", 22740, 70, getRandomColor(), 5))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(7374, 5)   (Matrix: progScrollText("Dont stop the music by Rihanna", 22740, 70, getRandomColor(), 5))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(16270, 4, 10)   (Matrix: progBlack(904, 10))</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progPalette(16270, 4, 10)   (Matrix: progBlack(904, 10))</t>
         </is>
@@ -572,13 +593,19 @@
           <t>ist gettin late</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(16270, 15, 1015, false)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16270, 15, 1015, false)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>who knew …</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(16270, 20, 510, true)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16270, 20, 510, true)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>do u know what u started</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(16275, 25, 7)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16275, 25, 7)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>chorus 1a: i wanna take it away</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(8136, 9, 30)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progPalette(8136, 9, 30)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>chorus 1a: i just cant refuse it</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8136, 8, 35)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8136, 8, 35)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>chorus 1b</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(8136, 37, 510)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8136, 37, 510)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>chorus: i just cant refuse it</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8136, 8, 40)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8136, 8, 40)</t>
         </is>
@@ -719,13 +782,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(16270, 45, 50, true, true)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16270, 45, 50, true, true)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>do u know what u started</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(16270, 50, 7)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16270, 50, 7)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>bridge: bass solo</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(15254, 55, 3000)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(15254, 55, 3000)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>STROBO</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1018, 60, 64, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1018, 60, 64, getRandomCRGB())</t>
         </is>
@@ -803,13 +890,19 @@
           <t>chorus 2a: i wanna take it away</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(8136, 65, 510)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8136, 65, 510)</t>
         </is>
@@ -824,13 +917,19 @@
           <t>chorus 2a: i just cant refuse it</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8136, 8, 70)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8136, 8, 70)</t>
         </is>
@@ -845,13 +944,19 @@
           <t>chorus 2a: i wanna take it away</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(8136, 75, 510)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8136, 75, 510)</t>
         </is>
@@ -866,13 +971,19 @@
           <t>chorus 2a: i just cant refuse it</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(8136, 510, 95, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8136, 510, 95, 5, 26, 5, true, 3)</t>
         </is>
@@ -887,13 +998,19 @@
           <t>chorus 4a: i wanna take it away</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+! nur im Excel - der alte Code geht hier schon in Schwarz</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -908,13 +1025,19 @@
           <t>chorus 4a: i just cant refuse it</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+! nur im Excel - der alte Code geht hier schon in Schwarz</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -929,13 +1052,19 @@
           <t>Bass Ende</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+! nur im Excel - der alte Code geht hier schon in Schwarz</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -955,10 +1084,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/DontStopTheMusic_v1/quelle/struktur.xlsx
+++ b/songs/DontStopTheMusic_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>

--- a/songs/DontStopTheMusic_v1/quelle/struktur.xlsx
+++ b/songs/DontStopTheMusic_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>118</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(7374, 5)   (Matrix: progScrollText("Dont stop the music by Rihanna", 22740, 70, getRandomColor(), 5))</t>
         </is>
@@ -573,12 +583,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, NEON, pumpt im Beat (pulse 40): Farbband über die ganze Bühne, das mit der Kick atmet.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progPalette(16270, 4, 10)   (Matrix: progBlack(904, 10))</t>
         </is>
@@ -600,12 +615,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, ROYAL: dezenter Puls im Beat (Zonen der Gitarre, Lichtschuss in den Lampen).</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16270, 15, 1015, false)</t>
         </is>
@@ -627,12 +647,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, ROYAL -&gt; Farbwanderung nach NEON: Bühnenhälften blitzen abwechselnd, eine Stufe mehr als der Part davor.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16270, 20, 510, true)</t>
         </is>
@@ -654,12 +679,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, SUNSET, darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 8 Takte) - Spannung bis zum Chorus. Letzter halber Takt weißer Strobo (tail 2 Beats).</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16275, 25, 7)</t>
         </is>
@@ -681,12 +711,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, NEON, Blinder auf den Einsatz (2 Beats). Fester Look für alle "take it away".</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progPalette(8136, 9, 30)</t>
         </is>
@@ -708,12 +743,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Einzelblitze bleiben (Szene Sparkle, NEON). Fester Look für alle "cant refuse it".</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8136, 8, 35)</t>
         </is>
@@ -735,12 +775,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, NEON, soft 30: ganze Bühne eine Farbe pro Beat, mit kurzer Blende statt hartem Sprung.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8136, 37, 510)</t>
         </is>
@@ -762,12 +807,13 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8136, 8, 40)</t>
         </is>
@@ -789,12 +835,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben, weich eingeblendet (fade, 4 Beats) - Ruhe nach dem Chorus.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16270, 45, 50, true, true)</t>
         </is>
@@ -816,12 +867,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal: Palette SUNSET + Glitzern baut sich auf.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16270, 50, 7)</t>
         </is>
@@ -843,12 +899,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Szene Solo Bass, SUNSET: zwei Kometen laufen um den Bass, alle anderen atmen dunkel. Übergang läuft über die Bühne zum Bass hin (stage_rl).</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(15254, 55, 3000)</t>
         </is>
@@ -870,12 +931,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Weißer Strobo statt Zufallsfarbe - härterer Absprung.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1018, 60, 64, getRandomCRGB())</t>
         </is>
@@ -897,12 +963,17 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, NEON, Blinder auf den Einsatz; Lampen blitzen weiß auf 2 und 4 (eine Stufe mehr als Chorus 1).</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8136, 65, 510)</t>
         </is>
@@ -924,12 +995,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, NEON. Auf der Matrix der Text "DONT STOP THE MUSIC" (ein Wort pro Beat) über der Szene.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8136, 8, 70)</t>
         </is>
@@ -951,12 +1027,17 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, SUNSET - ab hier kippt die Farbe ins Warme.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8136, 75, 510)</t>
         </is>
@@ -978,12 +1059,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, SUNSET, Text "DONT STOP THE MUSIC" wie oben.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8136, 510, 95, 5, 26, 5, true, 3)</t>
         </is>
@@ -1005,12 +1091,17 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Im alten Code schon Schwarz. Vorschlag: Szene Fire, FIRE - Höhepunkt, Blinder auf den Einsatz.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1032,12 +1123,17 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE; starker Blinder auf der letzten Viertel (Takt 100,75), klingt in "Bass Ende" aus (carry).</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1059,12 +1155,17 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Szene Solo Bass, RED, blendet über die letzten 2 Takte aus (fade_out 8 Beats).</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1084,10 +1185,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <f>$C$3</f>
         <v/>
       </c>
